--- a/outputs/q4/carrier_utilization.xlsx
+++ b/outputs/q4/carrier_utilization.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5999.5</v>
+        <v>4004.125</v>
       </c>
       <c r="D3" t="n">
         <v>6000</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.6673541666666667</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.620568780006</v>
       </c>
       <c r="D4" t="n">
         <v>6000</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999367614633343</v>
       </c>
     </row>
     <row r="5">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5999.500000000004</v>
+        <v>5999.678424832232</v>
       </c>
       <c r="D5" t="n">
         <v>6000</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9999464041387053</v>
       </c>
     </row>
     <row r="6">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5999.699999999997</v>
+        <v>5999.488639547033</v>
       </c>
       <c r="D7" t="n">
         <v>6000</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999499999999996</v>
+        <v>0.9999147732578388</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>6000</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6000</v>
+        <v>4000.159725338905</v>
       </c>
       <c r="D9" t="n">
         <v>6000</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.6666932875564842</v>
       </c>
     </row>
     <row r="10">
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5999.5</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>6000</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.289941917075</v>
       </c>
       <c r="D12" t="n">
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9998816569861793</v>
       </c>
     </row>
     <row r="13">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5999.500000000004</v>
+        <v>5984.601651487765</v>
       </c>
       <c r="D13" t="n">
         <v>6000</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9974336085812942</v>
       </c>
     </row>
     <row r="14">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.926548524303</v>
       </c>
       <c r="D15" t="n">
         <v>6000</v>
       </c>
       <c r="E15" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999877580873838</v>
       </c>
     </row>
     <row r="16">
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>6000</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6000</v>
+        <v>5360.274201852143</v>
       </c>
       <c r="D17" t="n">
         <v>6000</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.8933790336420239</v>
       </c>
     </row>
     <row r="18">
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D19" t="n">
         <v>6000</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="20">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.721362533371</v>
       </c>
       <c r="D20" t="n">
         <v>6000</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999535604222285</v>
       </c>
     </row>
     <row r="21">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5999.500000000004</v>
+        <v>5974.630810430146</v>
       </c>
       <c r="D21" t="n">
         <v>6000</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9957718017383577</v>
       </c>
     </row>
     <row r="22">
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.421000133298</v>
       </c>
       <c r="D23" t="n">
         <v>6000</v>
       </c>
       <c r="E23" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999035000222163</v>
       </c>
     </row>
     <row r="24">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>6000</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6000</v>
+        <v>4519.632315026693</v>
       </c>
       <c r="D25" t="n">
         <v>6000</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.7532720525044487</v>
       </c>
     </row>
     <row r="26">
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5999.5</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>6000</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9999166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.757464996043</v>
       </c>
       <c r="D28" t="n">
         <v>6000</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999595774993406</v>
       </c>
     </row>
     <row r="29">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5999.500000000004</v>
+        <v>5973.132669240483</v>
       </c>
       <c r="D29" t="n">
         <v>6000</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9955221115400804</v>
       </c>
     </row>
     <row r="30">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.391538575834</v>
       </c>
       <c r="D31" t="n">
         <v>6000</v>
       </c>
       <c r="E31" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998985897626389</v>
       </c>
     </row>
     <row r="32">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>6000</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6000</v>
+        <v>5825.390747617791</v>
       </c>
       <c r="D33" t="n">
         <v>6000</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.9708984579362985</v>
       </c>
     </row>
     <row r="34">
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D35" t="n">
         <v>6000</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.628530452401</v>
       </c>
       <c r="D36" t="n">
         <v>6000</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999380884087334</v>
       </c>
     </row>
     <row r="37">
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5999.500000000004</v>
+        <v>5961.200073454674</v>
       </c>
       <c r="D37" t="n">
         <v>6000</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.993533345575779</v>
       </c>
     </row>
     <row r="38">
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.903678313094</v>
       </c>
       <c r="D39" t="n">
         <v>6000</v>
       </c>
       <c r="E39" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999839463855157</v>
       </c>
     </row>
     <row r="40">
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>6000</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6000</v>
+        <v>4174.605085216756</v>
       </c>
       <c r="D41" t="n">
         <v>6000</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.6957675142027927</v>
       </c>
     </row>
     <row r="42">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D43" t="n">
         <v>6000</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.738952825064</v>
       </c>
       <c r="D44" t="n">
         <v>6000</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999564921375107</v>
       </c>
     </row>
     <row r="45">
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5999.500000000004</v>
+        <v>5999.588156513815</v>
       </c>
       <c r="D45" t="n">
         <v>6000</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9999313594189692</v>
       </c>
     </row>
     <row r="46">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.38446234693</v>
       </c>
       <c r="D47" t="n">
         <v>6000</v>
       </c>
       <c r="E47" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998974103911551</v>
       </c>
     </row>
     <row r="48">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>6000</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6000</v>
+        <v>4680.751146935066</v>
       </c>
       <c r="D49" t="n">
         <v>6000</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0.7801251911558442</v>
       </c>
     </row>
     <row r="50">
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D51" t="n">
         <v>6000</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="52">
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.614772686527</v>
       </c>
       <c r="D52" t="n">
         <v>6000</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999357954477546</v>
       </c>
     </row>
     <row r="53">
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5999.500000000004</v>
+        <v>5996.649022818263</v>
       </c>
       <c r="D53" t="n">
         <v>6000</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9994415038030439</v>
       </c>
     </row>
     <row r="54">
@@ -1472,13 +1472,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.612659952605</v>
       </c>
       <c r="D55" t="n">
         <v>6000</v>
       </c>
       <c r="E55" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999354433254342</v>
       </c>
     </row>
     <row r="56">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>6000</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6000</v>
+        <v>3943.190773591303</v>
       </c>
       <c r="D57" t="n">
         <v>6000</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.6571984622652172</v>
       </c>
     </row>
     <row r="58">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D59" t="n">
         <v>6000</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="60">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5999.900000000001</v>
+        <v>5976.024037538136</v>
       </c>
       <c r="D60" t="n">
         <v>6000</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9960040062563561</v>
       </c>
     </row>
     <row r="61">
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5999.500000000004</v>
+        <v>5950.843885093867</v>
       </c>
       <c r="D61" t="n">
         <v>6000</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9918073141823113</v>
       </c>
     </row>
     <row r="62">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.452139924885</v>
       </c>
       <c r="D63" t="n">
         <v>6000</v>
       </c>
       <c r="E63" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999086899874808</v>
       </c>
     </row>
     <row r="64">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>6000</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6000</v>
+        <v>3763.525069110401</v>
       </c>
       <c r="D65" t="n">
         <v>6000</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0.6272541781850669</v>
       </c>
     </row>
     <row r="66">
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D67" t="n">
         <v>6000</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="68">
@@ -1719,13 +1719,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5999.900000000001</v>
+        <v>5998.785763908246</v>
       </c>
       <c r="D68" t="n">
         <v>6000</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.999797627318041</v>
       </c>
     </row>
     <row r="69">
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5999.500000000004</v>
+        <v>5949.491865976473</v>
       </c>
       <c r="D69" t="n">
         <v>6000</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9915819776627455</v>
       </c>
     </row>
     <row r="70">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.550073439047</v>
       </c>
       <c r="D71" t="n">
         <v>6000</v>
       </c>
       <c r="E71" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999250122398412</v>
       </c>
     </row>
     <row r="72">
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
         <v>6000</v>
       </c>
       <c r="E72" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6000</v>
+        <v>4147.861527002583</v>
       </c>
       <c r="D73" t="n">
         <v>6000</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0.6913102545004305</v>
       </c>
     </row>
     <row r="74">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D75" t="n">
         <v>6000</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="76">
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.842087739024</v>
       </c>
       <c r="D76" t="n">
         <v>6000</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999736812898372</v>
       </c>
     </row>
     <row r="77">
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5999.500000000004</v>
+        <v>5955.934478174634</v>
       </c>
       <c r="D77" t="n">
         <v>6000</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.992655746362439</v>
       </c>
     </row>
     <row r="78">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.272734322423</v>
       </c>
       <c r="D79" t="n">
         <v>6000</v>
       </c>
       <c r="E79" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998787890537372</v>
       </c>
     </row>
     <row r="80">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>6000</v>
       </c>
       <c r="E80" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1966,13 +1966,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6000</v>
+        <v>4203.108562903818</v>
       </c>
       <c r="D81" t="n">
         <v>6000</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0.700518093817303</v>
       </c>
     </row>
     <row r="82">
@@ -2004,13 +2004,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D83" t="n">
         <v>6000</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="84">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.04127170748</v>
       </c>
       <c r="D84" t="n">
         <v>6000</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9998402119512466</v>
       </c>
     </row>
     <row r="85">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5999.500000000004</v>
+        <v>5995.217461620233</v>
       </c>
       <c r="D85" t="n">
         <v>6000</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9992029102700388</v>
       </c>
     </row>
     <row r="86">
@@ -2080,13 +2080,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.952829125295</v>
       </c>
       <c r="D87" t="n">
         <v>6000</v>
       </c>
       <c r="E87" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999921381875493</v>
       </c>
     </row>
     <row r="88">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
         <v>6000</v>
       </c>
       <c r="E88" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2118,13 +2118,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6000</v>
+        <v>4158.749562113812</v>
       </c>
       <c r="D89" t="n">
         <v>6000</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.6931249270189688</v>
       </c>
     </row>
     <row r="90">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D91" t="n">
         <v>6000</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="92">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.227715069864</v>
       </c>
       <c r="D92" t="n">
         <v>6000</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9998712858449773</v>
       </c>
     </row>
     <row r="93">
@@ -2194,13 +2194,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5999.500000000004</v>
+        <v>5996.823597233529</v>
       </c>
       <c r="D93" t="n">
         <v>6000</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9994705995389215</v>
       </c>
     </row>
     <row r="94">
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.968886588</v>
       </c>
       <c r="D95" t="n">
         <v>6000</v>
       </c>
       <c r="E95" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999948144313333</v>
       </c>
     </row>
     <row r="96">
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
         <v>6000</v>
       </c>
       <c r="E96" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6000</v>
+        <v>4150.413508351363</v>
       </c>
       <c r="D97" t="n">
         <v>6000</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0.6917355847252271</v>
       </c>
     </row>
     <row r="98">
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D99" t="n">
         <v>6000</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="100">
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5999.900000000001</v>
+        <v>5995.628261504808</v>
       </c>
       <c r="D100" t="n">
         <v>6000</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9992713769174679</v>
       </c>
     </row>
     <row r="101">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5999.500000000004</v>
+        <v>5949.773073012174</v>
       </c>
       <c r="D101" t="n">
         <v>6000</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.991628845502029</v>
       </c>
     </row>
     <row r="102">
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.38760959283</v>
       </c>
       <c r="D103" t="n">
         <v>6000</v>
       </c>
       <c r="E103" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998979349321383</v>
       </c>
     </row>
     <row r="104">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
         <v>6000</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6000</v>
+        <v>4136.006636385569</v>
       </c>
       <c r="D105" t="n">
         <v>6000</v>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0.6893344393975948</v>
       </c>
     </row>
     <row r="106">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D107" t="n">
         <v>6000</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="108">
@@ -2479,13 +2479,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5999.900000000001</v>
+        <v>5995.137594401168</v>
       </c>
       <c r="D108" t="n">
         <v>6000</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9991895990668613</v>
       </c>
     </row>
     <row r="109">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5999.500000000004</v>
+        <v>5930.310156267433</v>
       </c>
       <c r="D109" t="n">
         <v>6000</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9883850260445721</v>
       </c>
     </row>
     <row r="110">
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.257721296198</v>
       </c>
       <c r="D111" t="n">
         <v>6000</v>
       </c>
       <c r="E111" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998762868826996</v>
       </c>
     </row>
     <row r="112">
@@ -2555,13 +2555,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
         <v>6000</v>
       </c>
       <c r="E112" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6000</v>
+        <v>4203.592035291961</v>
       </c>
       <c r="D113" t="n">
         <v>6000</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.7005986725486602</v>
       </c>
     </row>
     <row r="114">
@@ -2612,13 +2612,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D115" t="n">
         <v>6000</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="116">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5999.900000000001</v>
+        <v>5998.567948690799</v>
       </c>
       <c r="D116" t="n">
         <v>6000</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9997613247817999</v>
       </c>
     </row>
     <row r="117">
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5999.500000000004</v>
+        <v>5995.829404510823</v>
       </c>
       <c r="D117" t="n">
         <v>6000</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9993049007518039</v>
       </c>
     </row>
     <row r="118">
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.399368592799</v>
       </c>
       <c r="D119" t="n">
         <v>6000</v>
       </c>
       <c r="E119" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998998947654665</v>
       </c>
     </row>
     <row r="120">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
         <v>6000</v>
       </c>
       <c r="E120" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6000</v>
+        <v>4147.12152362127</v>
       </c>
       <c r="D121" t="n">
         <v>6000</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0.691186920603545</v>
       </c>
     </row>
     <row r="122">
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D123" t="n">
         <v>6000</v>
       </c>
       <c r="E123" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="124">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>5999.900000000001</v>
+        <v>5989.037707807897</v>
       </c>
       <c r="D124" t="n">
         <v>6000</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9981729513013162</v>
       </c>
     </row>
     <row r="125">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5999.500000000004</v>
+        <v>5994.371949937061</v>
       </c>
       <c r="D125" t="n">
         <v>6000</v>
       </c>
       <c r="E125" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9990619916561768</v>
       </c>
     </row>
     <row r="126">
@@ -2840,13 +2840,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.210014407138</v>
       </c>
       <c r="D127" t="n">
         <v>6000</v>
       </c>
       <c r="E127" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998683357345231</v>
       </c>
     </row>
     <row r="128">
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
         <v>6000</v>
       </c>
       <c r="E128" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2878,13 +2878,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6000</v>
+        <v>4178.831042451878</v>
       </c>
       <c r="D129" t="n">
         <v>6000</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0.6964718404086463</v>
       </c>
     </row>
     <row r="130">
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D131" t="n">
         <v>6000</v>
       </c>
       <c r="E131" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="132">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.644713140278</v>
       </c>
       <c r="D132" t="n">
         <v>6000</v>
       </c>
       <c r="E132" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999407855233797</v>
       </c>
     </row>
     <row r="133">
@@ -2954,13 +2954,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5999.500000000004</v>
+        <v>5844.740954798537</v>
       </c>
       <c r="D133" t="n">
         <v>6000</v>
       </c>
       <c r="E133" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9741234924664228</v>
       </c>
     </row>
     <row r="134">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.492825610493</v>
       </c>
       <c r="D135" t="n">
         <v>6000</v>
       </c>
       <c r="E135" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999154709350822</v>
       </c>
     </row>
     <row r="136">
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
         <v>6000</v>
       </c>
       <c r="E136" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -3030,13 +3030,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>6000</v>
+        <v>4247.049307964378</v>
       </c>
       <c r="D137" t="n">
         <v>6000</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>0.7078415513273963</v>
       </c>
     </row>
     <row r="138">
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>5999.5</v>
+        <v>4004.125</v>
       </c>
       <c r="D139" t="n">
         <v>6000</v>
       </c>
       <c r="E139" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.6673541666666667</v>
       </c>
     </row>
     <row r="140">
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5999.900000000001</v>
+        <v>5925.399375461458</v>
       </c>
       <c r="D140" t="n">
         <v>6000</v>
       </c>
       <c r="E140" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9875665625769098</v>
       </c>
     </row>
     <row r="141">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5999.500000000004</v>
+        <v>5917.998413044035</v>
       </c>
       <c r="D141" t="n">
         <v>6000</v>
       </c>
       <c r="E141" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9863330688406725</v>
       </c>
     </row>
     <row r="142">
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5999.700000000006</v>
+        <v>5997.084549667901</v>
       </c>
       <c r="D143" t="n">
         <v>6000</v>
       </c>
       <c r="E143" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9995140916113169</v>
       </c>
     </row>
     <row r="144">
@@ -3163,13 +3163,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
         <v>6000</v>
       </c>
       <c r="E144" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>6000</v>
+        <v>2528.023621544357</v>
       </c>
       <c r="D145" t="n">
         <v>6000</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.4213372702573928</v>
       </c>
     </row>
     <row r="146">
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D147" t="n">
         <v>6000</v>
       </c>
       <c r="E147" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="148">
@@ -3239,13 +3239,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.910157075092</v>
       </c>
       <c r="D148" t="n">
         <v>6000</v>
       </c>
       <c r="E148" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999850261791819</v>
       </c>
     </row>
     <row r="149">
@@ -3258,13 +3258,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5999.500000000004</v>
+        <v>5995.83123662759</v>
       </c>
       <c r="D149" t="n">
         <v>6000</v>
       </c>
       <c r="E149" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9993052061045983</v>
       </c>
     </row>
     <row r="150">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5999.700000000006</v>
+        <v>5996.838182484356</v>
       </c>
       <c r="D151" t="n">
         <v>6000</v>
       </c>
       <c r="E151" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9994730304140594</v>
       </c>
     </row>
     <row r="152">
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D152" t="n">
         <v>6000</v>
       </c>
       <c r="E152" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6000</v>
+        <v>4042.607927087326</v>
       </c>
       <c r="D153" t="n">
         <v>6000</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0.6737679878478876</v>
       </c>
     </row>
     <row r="154">
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D155" t="n">
         <v>6000</v>
       </c>
       <c r="E155" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="156">
@@ -3391,13 +3391,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>5999.900000000001</v>
+        <v>5997.810170709617</v>
       </c>
       <c r="D156" t="n">
         <v>6000</v>
       </c>
       <c r="E156" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9996350284516028</v>
       </c>
     </row>
     <row r="157">
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5999.500000000004</v>
+        <v>5961.51143100505</v>
       </c>
       <c r="D157" t="n">
         <v>6000</v>
       </c>
       <c r="E157" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9935852385008417</v>
       </c>
     </row>
     <row r="158">
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.316178696487</v>
       </c>
       <c r="D159" t="n">
         <v>6000</v>
       </c>
       <c r="E159" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9998860297827478</v>
       </c>
     </row>
     <row r="160">
@@ -3467,13 +3467,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
         <v>6000</v>
       </c>
       <c r="E160" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>6000</v>
+        <v>4112.964742402058</v>
       </c>
       <c r="D161" t="n">
         <v>6000</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0.6854941237336762</v>
       </c>
     </row>
     <row r="162">
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D163" t="n">
         <v>6000</v>
       </c>
       <c r="E163" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="164">
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.814783807697</v>
       </c>
       <c r="D164" t="n">
         <v>6000</v>
       </c>
       <c r="E164" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9999691306346162</v>
       </c>
     </row>
     <row r="165">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5999.500000000004</v>
+        <v>5967.897413735156</v>
       </c>
       <c r="D165" t="n">
         <v>6000</v>
       </c>
       <c r="E165" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9946495689558593</v>
       </c>
     </row>
     <row r="166">
@@ -3600,13 +3600,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.423431911784</v>
       </c>
       <c r="D167" t="n">
         <v>6000</v>
       </c>
       <c r="E167" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999039053186307</v>
       </c>
     </row>
     <row r="168">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
         <v>6000</v>
       </c>
       <c r="E168" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -3638,13 +3638,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>6000</v>
+        <v>4100.230075790613</v>
       </c>
       <c r="D169" t="n">
         <v>6000</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0.6833716792984356</v>
       </c>
     </row>
     <row r="170">
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D171" t="n">
         <v>6000</v>
       </c>
       <c r="E171" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="172">
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5999.900000000001</v>
+        <v>5966.950335203833</v>
       </c>
       <c r="D172" t="n">
         <v>6000</v>
       </c>
       <c r="E172" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9944917225339721</v>
       </c>
     </row>
     <row r="173">
@@ -3714,13 +3714,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5999.500000000004</v>
+        <v>5989.096804257664</v>
       </c>
       <c r="D173" t="n">
         <v>6000</v>
       </c>
       <c r="E173" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9981828007096107</v>
       </c>
     </row>
     <row r="174">
@@ -3752,13 +3752,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5999.700000000006</v>
+        <v>5998.306043678625</v>
       </c>
       <c r="D175" t="n">
         <v>6000</v>
       </c>
       <c r="E175" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9997176739464374</v>
       </c>
     </row>
     <row r="176">
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
         <v>6000</v>
       </c>
       <c r="E176" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>6000</v>
+        <v>4159.80868038964</v>
       </c>
       <c r="D177" t="n">
         <v>6000</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0.6933014467316068</v>
       </c>
     </row>
     <row r="178">
@@ -3828,13 +3828,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D179" t="n">
         <v>6000</v>
       </c>
       <c r="E179" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="180">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5999.900000000001</v>
+        <v>5986.374048272775</v>
       </c>
       <c r="D180" t="n">
         <v>6000</v>
       </c>
       <c r="E180" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9977290080454626</v>
       </c>
     </row>
     <row r="181">
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5999.500000000004</v>
+        <v>5875.31160943094</v>
       </c>
       <c r="D181" t="n">
         <v>6000</v>
       </c>
       <c r="E181" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9792186015718233</v>
       </c>
     </row>
     <row r="182">
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.761031139103</v>
       </c>
       <c r="D183" t="n">
         <v>6000</v>
       </c>
       <c r="E183" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999601718565171</v>
       </c>
     </row>
     <row r="184">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
         <v>6000</v>
       </c>
       <c r="E184" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -3942,13 +3942,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>6000</v>
+        <v>4195.698217894578</v>
       </c>
       <c r="D185" t="n">
         <v>6000</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>0.6992830363157631</v>
       </c>
     </row>
     <row r="186">
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>5999.5</v>
+        <v>2402.475</v>
       </c>
       <c r="D187" t="n">
         <v>6000</v>
       </c>
       <c r="E187" t="n">
-        <v>0.9999166666666667</v>
+        <v>0.4004125000000001</v>
       </c>
     </row>
     <row r="188">
@@ -3999,13 +3999,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>5999.900000000001</v>
+        <v>5999.380211641434</v>
       </c>
       <c r="D188" t="n">
         <v>6000</v>
       </c>
       <c r="E188" t="n">
-        <v>0.9999833333333336</v>
+        <v>0.9998967019402389</v>
       </c>
     </row>
     <row r="189">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>5999.500000000004</v>
+        <v>5987.205499298287</v>
       </c>
       <c r="D189" t="n">
         <v>6000</v>
       </c>
       <c r="E189" t="n">
-        <v>0.9999166666666672</v>
+        <v>0.9978675832163811</v>
       </c>
     </row>
     <row r="190">
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5999.700000000006</v>
+        <v>5999.600022781357</v>
       </c>
       <c r="D191" t="n">
         <v>6000</v>
       </c>
       <c r="E191" t="n">
-        <v>0.999950000000001</v>
+        <v>0.9999333371302263</v>
       </c>
     </row>
     <row r="192">
@@ -4075,13 +4075,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3869.400000000001</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
         <v>6000</v>
       </c>
       <c r="E192" t="n">
-        <v>0.6449000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>6000</v>
+        <v>4094.173926983864</v>
       </c>
       <c r="D193" t="n">
         <v>6000</v>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0.6823623211639772</v>
       </c>
     </row>
   </sheetData>
